--- a/data/trans_dic/P19F$tarde-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,94; 36,92</t>
+          <t>27,12; 36,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 33,67</t>
+          <t>24,43; 33,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 33,4</t>
+          <t>26,55; 33,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,55; 36,63</t>
+          <t>28,6; 36,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 38,57</t>
+          <t>30,31; 38,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,17; 36,4</t>
+          <t>30,25; 36,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,51; 38,78</t>
+          <t>29,11; 39,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,73; 40,59</t>
+          <t>30,97; 40,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,39; 38,38</t>
+          <t>31,39; 38,47</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,84; 29,86</t>
+          <t>21,6; 29,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,37; 33,48</t>
+          <t>24,25; 33,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 30,26</t>
+          <t>24,04; 30,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 32,97</t>
+          <t>28,56; 33,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 34,25</t>
+          <t>29,96; 34,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 32,88</t>
+          <t>29,71; 32,95</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la tarde</t>
+          <t>Población que, al menos, se cepilla los dientes por la tarde (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97703; 133932</t>
+          <t>98390; 133432</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92153; 126665</t>
+          <t>91883; 126160</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199233; 246793</t>
+          <t>196192; 247024</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>160774; 206303</t>
+          <t>161085; 206249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164710; 208528</t>
+          <t>163827; 208966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>333032; 401789</t>
+          <t>333843; 398938</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118852; 156214</t>
+          <t>117258; 159072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>117926; 155773</t>
+          <t>118851; 156292</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>246870; 301917</t>
+          <t>246877; 302562</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98285; 134408</t>
+          <t>97233; 134695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107736; 148000</t>
+          <t>107174; 148068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>216718; 269998</t>
+          <t>214473; 267619</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>511174; 586444</t>
+          <t>508029; 588603</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>519259; 596831</t>
+          <t>522131; 603307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1042418; 1157740</t>
+          <t>1046212; 1160166</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$tarde-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$tarde-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,12; 36,79</t>
+          <t>26,86; 36,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,43; 33,54</t>
+          <t>24,57; 33,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 33,43</t>
+          <t>27,13; 33,92</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,6; 36,62</t>
+          <t>28,1; 35,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 38,66</t>
+          <t>30,46; 38,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 36,14</t>
+          <t>30,42; 36,36</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 39,49</t>
+          <t>29,06; 38,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,97; 40,73</t>
+          <t>31,01; 40,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,39; 38,47</t>
+          <t>31,1; 38,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 29,93</t>
+          <t>21,62; 29,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 33,5</t>
+          <t>24,59; 33,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,04; 30,0</t>
+          <t>24,19; 30,52</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,09</t>
+          <t>28,43; 33,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 34,62</t>
+          <t>29,82; 34,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,71; 32,95</t>
+          <t>29,95; 33,01</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98390; 133432</t>
+          <t>97434; 131772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91883; 126160</t>
+          <t>92421; 126861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>196192; 247024</t>
+          <t>200424; 250644</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161085; 206249</t>
+          <t>158237; 202458</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163827; 208966</t>
+          <t>164662; 210465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>333843; 398938</t>
+          <t>335781; 401283</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>117258; 159072</t>
+          <t>117043; 156543</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118851; 156292</t>
+          <t>119008; 155326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>246877; 302562</t>
+          <t>244592; 302697</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97233; 134695</t>
+          <t>97327; 133754</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107174; 148068</t>
+          <t>108716; 149627</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>214473; 267619</t>
+          <t>215844; 272242</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>508029; 588603</t>
+          <t>505745; 589137</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>522131; 603307</t>
+          <t>519547; 596318</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1046212; 1160166</t>
+          <t>1054609; 1162218</t>
         </is>
       </c>
     </row>
